--- a/Lista productos resumida.xlsx
+++ b/Lista productos resumida.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Tecnifer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Catalogo-Online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7FC91A-A780-4F3B-8311-F5CFAEB223C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545E77B4-6B2A-49B7-A334-C3E1645EAEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{4028B6C4-403F-4850-A2BB-374428BA98F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4028B6C4-403F-4850-A2BB-374428BA98F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="202">
   <si>
     <t>PRODUCTO</t>
   </si>
@@ -371,9 +371,6 @@
     <t xml:space="preserve">MATERIAS PRIMAS </t>
   </si>
   <si>
-    <t xml:space="preserve">ESENCIAS PERFUMERÍA </t>
-  </si>
-  <si>
     <t xml:space="preserve">DILUYENTE E - 43 </t>
   </si>
   <si>
@@ -624,6 +621,27 @@
   </si>
   <si>
     <t>PAÑOS ABSORBENTES 1 x 1 mt(120 gr/m2) 100 un.</t>
+  </si>
+  <si>
+    <t>ESENCIAS PERFUMERÍA FINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VASANA </t>
+  </si>
+  <si>
+    <t>Esencias para formulación de perfumes. Consultar por fragancias disponibles</t>
+  </si>
+  <si>
+    <t>Esencias para velas, sahumerios, lavandería, perfuminas, desodorantes para piso, etc. Consultar por fragancias disponibles</t>
+  </si>
+  <si>
+    <t>COLORANTE AL AGUA</t>
+  </si>
+  <si>
+    <t>COLORANTE A LA GRASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILICONAS WACKER </t>
   </si>
 </sst>
 </file>
@@ -647,7 +665,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,6 +720,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB97C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -728,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -741,12 +771,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFB97C7"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1881,7 +1918,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s">
         <v>110</v>
@@ -1892,7 +1929,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B86" t="s">
         <v>110</v>
@@ -1903,7 +1940,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B87" t="s">
         <v>110</v>
@@ -1911,7 +1948,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B88" t="s">
         <v>110</v>
@@ -1919,7 +1956,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B89" t="s">
         <v>110</v>
@@ -1927,7 +1964,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B90" t="s">
         <v>110</v>
@@ -1935,7 +1972,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B91" t="s">
         <v>110</v>
@@ -1943,7 +1980,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B92" t="s">
         <v>110</v>
@@ -1951,7 +1988,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B93" t="s">
         <v>110</v>
@@ -1959,7 +1996,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B94" t="s">
         <v>110</v>
@@ -1967,7 +2004,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B95" t="s">
         <v>110</v>
@@ -1975,7 +2012,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B96" t="s">
         <v>110</v>
@@ -1983,7 +2020,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B97" t="s">
         <v>110</v>
@@ -1991,7 +2028,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B98" t="s">
         <v>110</v>
@@ -1999,7 +2036,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B99" t="s">
         <v>110</v>
@@ -2007,7 +2044,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B100" t="s">
         <v>110</v>
@@ -2015,7 +2052,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B101" t="s">
         <v>110</v>
@@ -2023,7 +2060,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B102" t="s">
         <v>110</v>
@@ -2031,7 +2068,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B103" t="s">
         <v>110</v>
@@ -2039,7 +2076,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B104" t="s">
         <v>110</v>
@@ -2047,7 +2084,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B105" t="s">
         <v>110</v>
@@ -2055,7 +2092,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B106" t="s">
         <v>110</v>
@@ -2063,7 +2100,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B107" t="s">
         <v>110</v>
@@ -2071,7 +2108,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B108" t="s">
         <v>110</v>
@@ -2079,7 +2116,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B109" t="s">
         <v>110</v>
@@ -2087,7 +2124,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B110" t="s">
         <v>110</v>
@@ -2095,7 +2132,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B111" t="s">
         <v>110</v>
@@ -2103,7 +2140,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B112" t="s">
         <v>110</v>
@@ -2111,7 +2148,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B113" t="s">
         <v>110</v>
@@ -2119,7 +2156,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B114" t="s">
         <v>110</v>
@@ -2127,7 +2164,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B115" t="s">
         <v>110</v>
@@ -2135,7 +2172,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B116" t="s">
         <v>110</v>
@@ -2143,7 +2180,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B117" t="s">
         <v>110</v>
@@ -2151,7 +2188,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B118" t="s">
         <v>110</v>
@@ -2159,7 +2196,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B119" t="s">
         <v>110</v>
@@ -2167,7 +2204,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B120" t="s">
         <v>110</v>
@@ -2175,7 +2212,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B121" t="s">
         <v>110</v>
@@ -2183,7 +2220,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B122" t="s">
         <v>110</v>
@@ -2191,388 +2228,444 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B123" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B124" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C124" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B125" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B126" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C126" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B127" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C127" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B128" t="s">
         <v>158</v>
-      </c>
-      <c r="B128" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B129" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B131" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B132" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C132" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C133" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B134" t="s">
+        <v>158</v>
+      </c>
+      <c r="C134" t="s">
         <v>165</v>
-      </c>
-      <c r="B134" t="s">
-        <v>159</v>
-      </c>
-      <c r="C134" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B135" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B136" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B137" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B138" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B139" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B140" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B141" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B142" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B143" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B144" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B147" t="s">
         <v>179</v>
-      </c>
-      <c r="B147" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B148" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B149" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B150" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B151" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B152" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B154" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B155" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B156" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B157" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B158" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B159" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B160" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B160" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="B161" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B161" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+      <c r="B162" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B163" t="s">
+        <v>196</v>
+      </c>
+      <c r="C163" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B162" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="4"/>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="4"/>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="4"/>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="4"/>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="4"/>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="4"/>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="4"/>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="4"/>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="4"/>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="4"/>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B164" t="s">
+        <v>196</v>
+      </c>
+      <c r="C164" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="B165" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B166" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B167" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B168" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B169" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B170" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B171" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B172" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="4"/>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="4"/>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" s="4"/>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.3">

--- a/Lista productos resumida.xlsx
+++ b/Lista productos resumida.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Catalogo-Online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545E77B4-6B2A-49B7-A334-C3E1645EAEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B204A4-2809-49B0-8D42-6070D20A3BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4028B6C4-403F-4850-A2BB-374428BA98F3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{4028B6C4-403F-4850-A2BB-374428BA98F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="209">
   <si>
     <t>PRODUCTO</t>
   </si>
@@ -56,9 +56,6 @@
     <t xml:space="preserve">AVIA SOL 110 CONCENTRADO </t>
   </si>
   <si>
-    <t>AVIA SOL 110 BAJA ESPUMA CONCENTRADO</t>
-  </si>
-  <si>
     <t xml:space="preserve">SANITARIO INTEGRAL TF CONCENTRADO </t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t xml:space="preserve">TECNI QMO CONCENTRADO </t>
   </si>
   <si>
-    <t xml:space="preserve">TECNI QMO ELE CONCENTRADO </t>
-  </si>
-  <si>
     <t>TECNI S02 (SOLVENTE DIELÉCTRICO)</t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>X LT / X5 / X10 / X25 LTS</t>
   </si>
   <si>
-    <t>X 25 LTS</t>
-  </si>
-  <si>
     <t>X LT / X5 / X12 / X25 KG</t>
   </si>
   <si>
@@ -642,6 +633,93 @@
   </si>
   <si>
     <t xml:space="preserve">SILICONAS WACKER </t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN P/WEB</t>
+  </si>
+  <si>
+    <t>Desengrasante industrial de uso universal. Ideal para superficies contaminadas. Su pH alcalino garantiza un gran desempeño en superficies metálicas. Producto no abrasivo y biodegradable, no agresivo con la piel y no emite gases tóxicos. Recomendado para su uso en salas de máquinas, talleres, elevadores, cintas transportadoras etc. También recomendado para el mantenimiento de cubiertas de pesca, bodegas y mamparos. Producto altamente concentrado permite una dilucion de hasta 50 a 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desengrasante industrial de uso múltiple con aprobación de SENASA. A su alta capacidad de hidrolización de grasas y aceites se suma un gran poder bactericida, virucida y fungicida. Gran concentración, permite dilución hasta 1 en 50. Ideal para limpieza de frigoríficos de carnes rojas, aves, pescado, cocinas, depósitos, cintas transportadoras, bodegas, elementos de corte, entre otros.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desodorizante y desinfectante de uso industrial.  Excelente poder biocida, acción antibacteriana y antifúngica a pH neutro. Recomendado para todo tipo de industrias y necesidades. Su pH neutro lo hace compatible con cualquier tipo de material o superficie. Por su gran concentración es posible su dosificación de hasta 1:400 </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Desengrasante de uso industrial. Detersivo espumígeno ácido. Permite remover grasas neutras, desinfecta y remueve particulas de oxido. No corroe ni daña superficies metálicas haciéndolo ideal para limpieza de mesas de trabajo, tanques, tolvas, bandejas, cortinas sanitarias, paredes frisos, etc.. Producto aprobado por </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SENASA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ideal para su utilización en plantas procesadoras de alimento. Alta concentración, permite un gran margen de dilución</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Desengrasante industrial especialmente formulado para plantas procesadoras de alimentos. Detersivo espumígeno clorado. Por su pH básico regulado este prudcto logra hidrolizar grasas y aceites pesados a la vez que las disuelven para lograr la remoción completa. Potente desengrasante con acción desinfectante ideal para todo tipo de superficies, altamente concentrado permitiendo una gran dilución y un gran resultado en poco tiempo. Producto aprobado por </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SENASA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>para su utilización en la industria alimentaria.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Desoxidante y fosfatizante para todo tipo de metales. Captura y disuelve los óxidos de hierro eliminando rastros de herrumbre. Deposita una fina capa de fosfato que mejora la adherencia para pinturas y recubrimientos. Al mismo tiempo posee una enérgica acción desengrasante que evita pasos de limpieza extra. Producto altamente concentrado, con resultados probados en cubiertas y superficies de embarcaciones</t>
+  </si>
+  <si>
+    <t>Desodorizante de acción intensiva. Desarrollado específicamente para la remoción de olores desagradables en ambientes cerrados, como baños, vestuarios, desagües sépticos, depósitos etc. Potente acción bactericida y fungicida que previene la proliferación de microorganismos que generan olores molestos. No ataca ni decolora superficies delicadas como plasticos y gomas, por lo que se recominenda para su uso en cañerías y sistemas de bombeo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solvente dieléctrico de alto punto de inflamación. Solvente desengrasante ideal para limpieza de componentes eléctricos y electrónicos en frío. Formulado con una selección de solventes de altísima calidad, el producto posee un alto punto de inflamación y una tensión de ruptura excepcionalmente elevadas. Se evapora sin dejar residuos y no requiere limpieza posterior. Especialmente indicado para limpieza de equipamiento eléctrico, bobinas, sistemas electrónicos, entre otros. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desengrasante industrial. Desarrollado específicamente para el tratamiento y mantenimiento de sentinas. Desprende y ablanda la suciedad, manteniéndola en su estado de suspensión, actuando el desengrasante como elemento antidepositante y eliminándolo por arrastre. Elimina peligro de incendios y no ataca materiales como madera, hierro, bronce, etc. </t>
   </si>
 </sst>
 </file>
@@ -733,7 +811,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -754,11 +832,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -773,6 +862,9 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1092,15 +1184,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319BC528-4F8B-4A57-A715-E0E8758B6C0D}">
-  <dimension ref="A1:D199"/>
+  <dimension ref="A1:D197"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.88671875" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" customWidth="1"/>
     <col min="3" max="3" width="38.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1110,8 +1203,11 @@
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -1119,10 +1215,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -1130,10 +1229,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1141,10 +1243,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1152,10 +1257,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -1163,10 +1271,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1174,10 +1285,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -1185,10 +1299,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -1198,8 +1315,11 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
@@ -1207,12 +1327,15 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1221,40 +1344,40 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>24</v>
       </c>
@@ -1262,18 +1385,18 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -1284,317 +1407,317 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>28</v>
+      <c r="A18" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" t="s">
         <v>68</v>
-      </c>
-      <c r="B55" t="s">
-        <v>71</v>
       </c>
       <c r="C55" t="s">
         <v>69</v>
@@ -1602,24 +1725,24 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
         <v>73</v>
-      </c>
-      <c r="B57" t="s">
-        <v>71</v>
-      </c>
-      <c r="C57" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1627,10 +1750,10 @@
         <v>74</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1638,76 +1761,76 @@
         <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1715,7 +1838,7 @@
         <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
         <v>84</v>
@@ -1726,10 +1849,10 @@
         <v>85</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1737,21 +1860,21 @@
         <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
         <v>88</v>
-      </c>
-      <c r="B69" t="s">
-        <v>71</v>
-      </c>
-      <c r="C69" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1759,54 +1882,57 @@
         <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C71" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" t="s">
         <v>96</v>
       </c>
-      <c r="B74" t="s">
-        <v>71</v>
-      </c>
-      <c r="C74" t="s">
-        <v>97</v>
+      <c r="D74" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1814,24 +1940,27 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="D75" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C76" t="s">
+        <v>96</v>
+      </c>
+      <c r="D76" t="s">
         <v>100</v>
-      </c>
-      <c r="B76" t="s">
-        <v>71</v>
-      </c>
-      <c r="C76" t="s">
-        <v>99</v>
-      </c>
-      <c r="D76" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1839,13 +1968,7 @@
         <v>101</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
-      </c>
-      <c r="C77" t="s">
-        <v>99</v>
-      </c>
-      <c r="D77" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -1853,388 +1976,388 @@
         <v>102</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
-      </c>
-      <c r="C78" t="s">
-        <v>99</v>
-      </c>
-      <c r="D78" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
+      </c>
+      <c r="C81" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B81" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>107</v>
+      </c>
+      <c r="C82" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
-        <v>108</v>
+      <c r="A83" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C83" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="s">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>110</v>
-      </c>
-      <c r="C85" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" t="s">
-        <v>110</v>
-      </c>
-      <c r="C86" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B87" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B94" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B96" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B102" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B103" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B105" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B107" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B113" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B116" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B117" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B118" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B119" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B120" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B121" t="s">
         <v>145</v>
       </c>
-      <c r="B120" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B121" t="s">
-        <v>110</v>
+      <c r="C121" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="7" t="s">
+      <c r="A122" s="8" t="s">
         <v>147</v>
       </c>
       <c r="B122" t="s">
-        <v>110</v>
+        <v>145</v>
+      </c>
+      <c r="C122" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B123" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C123" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -2242,7 +2365,7 @@
         <v>150</v>
       </c>
       <c r="B124" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C124" t="s">
         <v>152</v>
@@ -2250,35 +2373,29 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B125" t="s">
+        <v>145</v>
+      </c>
+      <c r="C125" t="s">
         <v>151</v>
       </c>
-      <c r="B125" t="s">
-        <v>148</v>
-      </c>
-      <c r="C125" t="s">
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="9" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="8" t="s">
-        <v>153</v>
-      </c>
       <c r="B126" t="s">
-        <v>148</v>
-      </c>
-      <c r="C126" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="9" t="s">
         <v>156</v>
       </c>
       <c r="B127" t="s">
-        <v>148</v>
-      </c>
-      <c r="C127" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -2286,42 +2403,48 @@
         <v>157</v>
       </c>
       <c r="B128" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B129" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B130" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="C130" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B131" t="s">
-        <v>158</v>
+        <v>155</v>
+      </c>
+      <c r="C131" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B132" t="s">
+        <v>155</v>
+      </c>
+      <c r="C132" t="s">
         <v>162</v>
-      </c>
-      <c r="B132" t="s">
-        <v>158</v>
-      </c>
-      <c r="C132" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -2329,117 +2452,111 @@
         <v>163</v>
       </c>
       <c r="B133" t="s">
-        <v>158</v>
-      </c>
-      <c r="C133" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
-      </c>
-      <c r="C134" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B135" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B136" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B137" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B138" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B139" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B140" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B141" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B142" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B143" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="9" t="s">
-        <v>174</v>
+      <c r="A145" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="B145" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="9" t="s">
-        <v>175</v>
+      <c r="A146" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
@@ -2447,214 +2564,204 @@
         <v>178</v>
       </c>
       <c r="B147" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B148" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B149" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B150" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B151" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B153" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B154" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B155" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B156" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B157" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B158" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B159" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B160" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B161" t="s">
+        <v>193</v>
+      </c>
+      <c r="C161" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B160" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="3" t="s">
+      <c r="B162" t="s">
         <v>193</v>
       </c>
-      <c r="B161" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="3" t="s">
+      <c r="C162" t="s">
         <v>194</v>
-      </c>
-      <c r="B162" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" s="10" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="B163" t="s">
-        <v>196</v>
-      </c>
-      <c r="C163" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B164" t="s">
-        <v>196</v>
-      </c>
-      <c r="C164" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="10" t="s">
-        <v>199</v>
+      <c r="A165" s="11" t="s">
+        <v>117</v>
       </c>
       <c r="B165" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="10" t="s">
-        <v>200</v>
+      <c r="A166" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="B166" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B167" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="11" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B168" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" s="11" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B169" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B170" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B171" t="s">
-        <v>201</v>
-      </c>
+      <c r="A171" s="4"/>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B172" t="s">
-        <v>201</v>
-      </c>
+      <c r="A172" s="4"/>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
@@ -2730,12 +2837,6 @@
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A198" s="4"/>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A199" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
